--- a/Histórico de culturas.xlsx
+++ b/Histórico de culturas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1cc81c05594695/Dashboards/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{B663FA9D-63D9-4817-B51A-83BC726D2529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FB88D92-0AF1-49EF-A8C4-FB84A131E1E0}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{B663FA9D-63D9-4817-B51A-83BC726D2529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B4D53B3-BE99-4CEF-9B6C-6B954271BB9E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC402824-E070-4638-AB0F-B9DF5E3FF754}"/>
   </bookViews>
@@ -2412,7 +2412,7 @@
         <v>23.876519999999999</v>
       </c>
       <c r="T12" s="10">
-        <v>17.880022946394135</v>
+        <v>18.22</v>
       </c>
       <c r="U12" s="10">
         <f>1511829/38000</f>

--- a/Histórico de culturas.xlsx
+++ b/Histórico de culturas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1cc81c05594695/Dashboards/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="8_{B663FA9D-63D9-4817-B51A-83BC726D2529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1614CE4-DDA2-4AB3-8C31-3AF28E2CA3D7}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="8_{B663FA9D-63D9-4817-B51A-83BC726D2529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{590CE95A-87DC-458C-BC82-EE5F7917CEE2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC402824-E070-4638-AB0F-B9DF5E3FF754}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="456">
   <si>
     <t>quinta</t>
   </si>
@@ -1398,6 +1398,18 @@
   </si>
   <si>
     <t>SAMBLAS 4</t>
+  </si>
+  <si>
+    <t>Tamanho</t>
+  </si>
+  <si>
+    <t>Grande</t>
+  </si>
+  <si>
+    <t>Mini</t>
+  </si>
+  <si>
+    <t>Todas</t>
   </si>
 </sst>
 </file>
@@ -1445,20 +1457,11 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1501,10 +1504,10 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1524,10 +1527,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1850,7 +1849,7 @@
     <col min="19" max="19" width="7.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="17.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="23" max="16384" width="11.42578125" style="7"/>
   </cols>
   <sheetData>
@@ -1892,27 +1891,30 @@
         <v>10</v>
       </c>
       <c r="N1" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="O1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1951,12 +1953,14 @@
         <v>95.97503912363068</v>
       </c>
       <c r="M2" s="6">
-        <v>2016</v>
-      </c>
-      <c r="N2" s="12">
-        <v>15</v>
-      </c>
-      <c r="O2" s="10"/>
+        <v>2018</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="O2" s="10">
+        <v>22.524891045454545</v>
+      </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
       <c r="R2" s="10"/>
@@ -2000,12 +2004,14 @@
         <v>105.34243827160493</v>
       </c>
       <c r="M3" s="6">
-        <v>2017</v>
-      </c>
-      <c r="N3" s="10">
-        <v>8</v>
-      </c>
-      <c r="O3" s="10"/>
+        <v>2018</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="O3" s="10">
+        <v>21.803595772357721</v>
+      </c>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
@@ -2051,10 +2057,12 @@
       <c r="M4" s="6">
         <v>2018</v>
       </c>
-      <c r="N4" s="10">
-        <v>22</v>
-      </c>
-      <c r="O4" s="10"/>
+      <c r="N4" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="O4" s="10">
+        <v>23.036074226804121</v>
+      </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
@@ -2100,10 +2108,12 @@
       <c r="M5" s="6">
         <v>2019</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="O5" s="10">
         <v>13</v>
       </c>
-      <c r="O5" s="10"/>
       <c r="P5" s="10"/>
       <c r="Q5" s="10"/>
       <c r="R5" s="10"/>
@@ -2147,12 +2157,14 @@
         <v>102.10125337920866</v>
       </c>
       <c r="M6" s="6">
-        <v>2020</v>
-      </c>
-      <c r="N6" s="10">
-        <v>21</v>
-      </c>
-      <c r="O6" s="10"/>
+        <v>2019</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="O6" s="10">
+        <v>18.805777238834953</v>
+      </c>
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
@@ -2196,21 +2208,17 @@
         <v>115.9375</v>
       </c>
       <c r="M7" s="6">
-        <v>2021</v>
-      </c>
-      <c r="N7" s="10">
-        <v>27.832124615384615</v>
-      </c>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10">
-        <v>17.846075714285714</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>9.1619093249999999</v>
-      </c>
-      <c r="R7" s="10">
-        <v>14.619892500000002</v>
-      </c>
+        <v>2019</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="O7" s="10">
+        <v>9.0406175182481778</v>
+      </c>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
       <c r="U7" s="10"/>
@@ -2251,30 +2259,20 @@
         <v>87.148864592094199</v>
       </c>
       <c r="M8" s="6">
-        <v>2022</v>
-      </c>
-      <c r="N8" s="10">
-        <v>28.775224384906121</v>
-      </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10">
-        <v>25.389915500000004</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>21.834218939393939</v>
-      </c>
-      <c r="R8" s="10">
-        <v>13.345863250000001</v>
-      </c>
-      <c r="S8" s="10">
-        <v>22.790868595041324</v>
-      </c>
-      <c r="T8" s="10">
-        <v>21.219038352272722</v>
-      </c>
-      <c r="U8" s="10">
-        <v>3.9488084210526315</v>
-      </c>
+        <v>2020</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="O8" s="10">
+        <v>21</v>
+      </c>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
       <c r="V8" s="10"/>
     </row>
     <row r="9" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2312,30 +2310,20 @@
         <v>133.4257494368394</v>
       </c>
       <c r="M9" s="6">
-        <v>2023</v>
-      </c>
-      <c r="N9" s="10">
-        <v>31.645020900737237</v>
-      </c>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10">
-        <v>26.417962571428571</v>
-      </c>
-      <c r="Q9" s="10">
-        <v>22.356989875</v>
-      </c>
-      <c r="R9" s="10">
-        <v>20.420041000000001</v>
-      </c>
-      <c r="S9" s="10">
-        <v>18.248904958677688</v>
-      </c>
-      <c r="T9" s="10">
-        <v>13.352525641025643</v>
-      </c>
-      <c r="U9" s="10">
-        <v>23.281768421052636</v>
-      </c>
+        <v>2020</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="O9" s="10">
+        <v>20.240749509112685</v>
+      </c>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
       <c r="V9" s="10"/>
     </row>
     <row r="10" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2373,30 +2361,20 @@
         <v>126.80208333333333</v>
       </c>
       <c r="M10" s="6">
-        <v>2024</v>
-      </c>
-      <c r="N10" s="10">
-        <v>33.642821769230771</v>
-      </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10">
-        <v>24.493246000000003</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>22.056638</v>
-      </c>
-      <c r="R10" s="10">
-        <v>12.045852249999999</v>
-      </c>
-      <c r="S10" s="10">
-        <v>16.830454545454547</v>
-      </c>
-      <c r="T10" s="10">
-        <v>25.23423076923077</v>
-      </c>
-      <c r="U10" s="10">
-        <v>25.799747368421052</v>
-      </c>
+        <v>2020</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="O10" s="10">
+        <v>10.545403225806449</v>
+      </c>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
       <c r="V10" s="10"/>
     </row>
     <row r="11" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2434,32 +2412,26 @@
         <v>79.36323970548132</v>
       </c>
       <c r="M11" s="6">
-        <v>2025</v>
-      </c>
-      <c r="N11" s="10">
-        <v>36.596405153846156</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0</v>
-      </c>
-      <c r="P11" s="10">
-        <v>23.047109000000003</v>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="O11" s="12">
+        <v>27.832124615384615</v>
+      </c>
+      <c r="P11" s="10"/>
       <c r="Q11" s="10">
-        <v>21.4094879875</v>
+        <v>17.846075714285714</v>
       </c>
       <c r="R11" s="10">
-        <v>20.682577000000002</v>
+        <v>8.2664759726027395</v>
       </c>
       <c r="S11" s="10">
-        <v>18.489404958677685</v>
-      </c>
-      <c r="T11" s="10">
-        <v>15.49898717948718</v>
-      </c>
-      <c r="U11" s="10">
-        <v>28.443348421052633</v>
-      </c>
+        <v>14.619892500000002</v>
+      </c>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
       <c r="V11" s="10"/>
     </row>
     <row r="12" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2497,30 +2469,24 @@
         <v>134.80628272251309</v>
       </c>
       <c r="M12" s="6">
-        <v>2026</v>
-      </c>
-      <c r="N12" s="10">
-        <v>31.630769230769232</v>
-      </c>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10">
-        <v>23.419628571428571</v>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="O12" s="10">
+        <v>34.914466743648958</v>
+      </c>
+      <c r="P12" s="10"/>
       <c r="Q12" s="10">
-        <v>23.489987499999998</v>
+        <v>19.616028310502283</v>
       </c>
       <c r="R12" s="10">
-        <v>18.736599999999999</v>
-      </c>
-      <c r="S12" s="10">
-        <v>23.876519999999999</v>
-      </c>
-      <c r="T12" s="10">
-        <v>18.22</v>
-      </c>
-      <c r="U12" s="10">
-        <v>39.784973684210527</v>
-      </c>
+        <v>23.946056757660003</v>
+      </c>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
       <c r="V12" s="10"/>
     </row>
     <row r="13" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2557,8 +2523,28 @@
       <c r="K13" s="9">
         <v>92.285357247868262</v>
       </c>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
+      <c r="M13" s="6">
+        <v>2021</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="O13" s="10">
+        <v>13.751276497695853</v>
+      </c>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10">
+        <v>11.491655737704919</v>
+      </c>
+      <c r="R13" s="10">
+        <v>4.8552449016751646</v>
+      </c>
+      <c r="S13" s="10">
+        <v>14.619892500000002</v>
+      </c>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
     </row>
     <row r="14" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
@@ -2594,8 +2580,34 @@
       <c r="K14" s="9">
         <v>100.23474178403755</v>
       </c>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
+      <c r="M14" s="6">
+        <v>2022</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="O14" s="10">
+        <v>28.775224384906121</v>
+      </c>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10">
+        <v>24.996092900763362</v>
+      </c>
+      <c r="R14" s="10">
+        <v>19.122325504246284</v>
+      </c>
+      <c r="S14" s="10">
+        <v>13.688064871794873</v>
+      </c>
+      <c r="T14" s="10">
+        <v>22.322273553719011</v>
+      </c>
+      <c r="U14" s="10">
+        <v>22.848262215909088</v>
+      </c>
+      <c r="V14" s="10">
+        <v>3.9488084210526315</v>
+      </c>
     </row>
     <row r="15" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
@@ -2631,8 +2643,32 @@
       <c r="K15" s="9">
         <v>139.22529644268775</v>
       </c>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
+      <c r="M15" s="6">
+        <v>2022</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="O15" s="10">
+        <v>44.755207278481009</v>
+      </c>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10">
+        <v>26.871600337467001</v>
+      </c>
+      <c r="R15" s="10">
+        <v>19.137562416998673</v>
+      </c>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10">
+        <v>22.790868595041324</v>
+      </c>
+      <c r="U15" s="10">
+        <v>24.329320846905535</v>
+      </c>
+      <c r="V15" s="10">
+        <v>5.96</v>
+      </c>
     </row>
     <row r="16" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
@@ -2668,10 +2704,32 @@
       <c r="K16" s="9">
         <v>108.35922171353828</v>
       </c>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-    </row>
-    <row r="17" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M16" s="6">
+        <v>2022</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="O16" s="10">
+        <v>13.359865269461078</v>
+      </c>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10">
+        <v>15.044151240010866</v>
+      </c>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10">
+        <v>13.345863250000001</v>
+      </c>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10">
+        <v>12.74</v>
+      </c>
+      <c r="V16" s="10">
+        <v>3.3070813662871426</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>17</v>
       </c>
@@ -2705,10 +2763,36 @@
       <c r="K17" s="9">
         <v>171.35638297872342</v>
       </c>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-    </row>
-    <row r="18" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M17" s="6">
+        <v>2023</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="O17" s="10">
+        <v>31.645020900737237</v>
+      </c>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10">
+        <v>26.417962571428571</v>
+      </c>
+      <c r="R17" s="10">
+        <v>22.356989875</v>
+      </c>
+      <c r="S17" s="10">
+        <v>25.925180236113405</v>
+      </c>
+      <c r="T17" s="10">
+        <v>15.961381118881121</v>
+      </c>
+      <c r="U17" s="10">
+        <v>13.352525641025643</v>
+      </c>
+      <c r="V17" s="10">
+        <v>23.281768421052636</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>11</v>
       </c>
@@ -2742,10 +2826,36 @@
       <c r="K18" s="9">
         <v>118.05918901242643</v>
       </c>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-    </row>
-    <row r="19" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M18" s="6">
+        <v>2023</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="O18" s="10">
+        <v>33.958846645454543</v>
+      </c>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10">
+        <v>27.332939222746461</v>
+      </c>
+      <c r="R18" s="10">
+        <v>22.983997184986595</v>
+      </c>
+      <c r="S18" s="10">
+        <v>32.24</v>
+      </c>
+      <c r="T18" s="10">
+        <v>16.516254348666408</v>
+      </c>
+      <c r="U18" s="10">
+        <v>13.180618503118504</v>
+      </c>
+      <c r="V18" s="10">
+        <v>28.017012448132785</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>13</v>
       </c>
@@ -2779,10 +2889,36 @@
       <c r="K19" s="9">
         <v>79.512183704141719</v>
       </c>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-    </row>
-    <row r="20" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M19" s="6">
+        <v>2023</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="O19" s="10">
+        <v>20.3085515</v>
+      </c>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10">
+        <v>15.83</v>
+      </c>
+      <c r="R19" s="10">
+        <v>13.695</v>
+      </c>
+      <c r="S19" s="10">
+        <v>16.672226032094365</v>
+      </c>
+      <c r="T19" s="10">
+        <v>7.8412868632707777</v>
+      </c>
+      <c r="U19" s="10">
+        <v>14.147596153846152</v>
+      </c>
+      <c r="V19" s="10">
+        <v>15.911302475780413</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
@@ -2816,10 +2952,36 @@
       <c r="K20" s="9">
         <v>101.69331395348836</v>
       </c>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-    </row>
-    <row r="21" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M20" s="6">
+        <v>2024</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="O20" s="10">
+        <v>33.642821769230771</v>
+      </c>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10">
+        <v>24.493246000000003</v>
+      </c>
+      <c r="R20" s="10">
+        <v>22.056638</v>
+      </c>
+      <c r="S20" s="10">
+        <v>12.045852249999999</v>
+      </c>
+      <c r="T20" s="10">
+        <v>16.830454545454547</v>
+      </c>
+      <c r="U20" s="10">
+        <v>25.23423076923077</v>
+      </c>
+      <c r="V20" s="10">
+        <v>25.799747368421052</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>11</v>
       </c>
@@ -2853,10 +3015,34 @@
       <c r="K21" s="9">
         <v>73.120300751879697</v>
       </c>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-    </row>
-    <row r="22" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M21" s="6">
+        <v>2024</v>
+      </c>
+      <c r="N21" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="O21" s="10">
+        <v>37.35192</v>
+      </c>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10">
+        <v>27.332939222746461</v>
+      </c>
+      <c r="R21" s="10">
+        <v>22.056638</v>
+      </c>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10">
+        <v>16.886537664132689</v>
+      </c>
+      <c r="U21" s="10">
+        <v>25.993444816053511</v>
+      </c>
+      <c r="V21" s="10">
+        <v>28.083116883116883</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>14</v>
       </c>
@@ -2890,10 +3076,34 @@
       <c r="K22" s="9">
         <v>53.859739263803682</v>
       </c>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-    </row>
-    <row r="23" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M22" s="6">
+        <v>2024</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="O22" s="10">
+        <v>21.2684</v>
+      </c>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10">
+        <v>15.83</v>
+      </c>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10">
+        <v>12.045852249999999</v>
+      </c>
+      <c r="T22" s="10">
+        <v>10.824</v>
+      </c>
+      <c r="U22" s="10">
+        <v>7.7723076923076926</v>
+      </c>
+      <c r="V22" s="10">
+        <v>24.345692625775328</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>11</v>
       </c>
@@ -2927,10 +3137,36 @@
       <c r="K23" s="9">
         <v>76.355263157894726</v>
       </c>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-    </row>
-    <row r="24" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M23" s="6">
+        <v>2025</v>
+      </c>
+      <c r="N23" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="O23" s="10">
+        <v>36.596405153846156</v>
+      </c>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10">
+        <v>23.047109000000003</v>
+      </c>
+      <c r="R23" s="10">
+        <v>21.4094879875</v>
+      </c>
+      <c r="S23" s="10">
+        <v>21.212899487179488</v>
+      </c>
+      <c r="T23" s="10">
+        <v>18.489404958677685</v>
+      </c>
+      <c r="U23" s="10">
+        <v>15.49898717948718</v>
+      </c>
+      <c r="V23" s="10">
+        <v>28.443348421052633</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>14</v>
       </c>
@@ -2964,10 +3200,36 @@
       <c r="K24" s="9">
         <v>56.628409090909081</v>
       </c>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-    </row>
-    <row r="25" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M24" s="6">
+        <v>2025</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="O24" s="10">
+        <v>39.229893245778612</v>
+      </c>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10">
+        <v>23.047109000000003</v>
+      </c>
+      <c r="R24" s="10">
+        <v>21.4094879875</v>
+      </c>
+      <c r="S24" s="10">
+        <v>18.837375609756098</v>
+      </c>
+      <c r="T24" s="10">
+        <v>18.489404958677685</v>
+      </c>
+      <c r="U24" s="10">
+        <v>15.49898717948718</v>
+      </c>
+      <c r="V24" s="10">
+        <v>29.631240190488967</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>16</v>
       </c>
@@ -3001,10 +3263,28 @@
       <c r="K25" s="9">
         <v>148.98009338903907</v>
       </c>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-    </row>
-    <row r="26" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M25" s="6">
+        <v>2025</v>
+      </c>
+      <c r="N25" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="O25" s="10">
+        <v>24.332381973581967</v>
+      </c>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10">
+        <v>22.622404102564104</v>
+      </c>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="10">
+        <v>27.676370880429602</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>15</v>
       </c>
@@ -3038,10 +3318,36 @@
       <c r="K26" s="9">
         <v>154.19405940594058</v>
       </c>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-    </row>
-    <row r="27" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M26" s="6">
+        <v>2026</v>
+      </c>
+      <c r="N26" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="O26" s="10">
+        <v>31.630769230769232</v>
+      </c>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10">
+        <v>23.419628571428571</v>
+      </c>
+      <c r="R26" s="10">
+        <v>23.489987499999998</v>
+      </c>
+      <c r="S26" s="10">
+        <v>18.736599999999999</v>
+      </c>
+      <c r="T26" s="10">
+        <v>23.876519999999999</v>
+      </c>
+      <c r="U26" s="10">
+        <v>17.695974971772674</v>
+      </c>
+      <c r="V26" s="10">
+        <v>39.784973684210527</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>11</v>
       </c>
@@ -3075,10 +3381,36 @@
       <c r="K27" s="9">
         <v>93.900382086675151</v>
       </c>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-    </row>
-    <row r="28" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M27" s="6">
+        <v>2026</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="O27" s="10">
+        <v>33.389207258834766</v>
+      </c>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10">
+        <v>23.419628571428571</v>
+      </c>
+      <c r="R27" s="10">
+        <v>23.489987499999998</v>
+      </c>
+      <c r="S27" s="10">
+        <v>14.868798536585366</v>
+      </c>
+      <c r="T27" s="10">
+        <v>23.876519999999999</v>
+      </c>
+      <c r="U27" s="10">
+        <v>17.695974971772674</v>
+      </c>
+      <c r="V27" s="10">
+        <v>52.050000000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>11</v>
       </c>
@@ -3112,10 +3444,28 @@
       <c r="K28" s="9">
         <v>101.13300663816774</v>
       </c>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-    </row>
-    <row r="29" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M28" s="6">
+        <v>2026</v>
+      </c>
+      <c r="N28" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="O28" s="10">
+        <v>24.362964426877472</v>
+      </c>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10">
+        <v>23.291692307692308</v>
+      </c>
+      <c r="T28" s="10"/>
+      <c r="U28" s="10"/>
+      <c r="V28" s="10">
+        <v>26.71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>13</v>
       </c>
@@ -3152,7 +3502,7 @@
       <c r="N29" s="10"/>
       <c r="O29" s="10"/>
     </row>
-    <row r="30" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
         <v>13</v>
       </c>
@@ -3189,7 +3539,7 @@
       <c r="N30" s="10"/>
       <c r="O30" s="10"/>
     </row>
-    <row r="31" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
         <v>11</v>
       </c>
@@ -3223,7 +3573,7 @@
       <c r="N31" s="10"/>
       <c r="O31" s="10"/>
     </row>
-    <row r="32" spans="1:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>11</v>
       </c>
